--- a/pautas_excel/25 DE SEPTIEMBRE.xlsx
+++ b/pautas_excel/25 DE SEPTIEMBRE.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WhatsApp Image 2026-09-24 at 12" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Viernes 25 septiembre 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1282,15 +1282,7 @@
               <color rgb="00C00000"/>
               <sz val="11"/>
             </rPr>
-            <t>20228</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial Narrow"/>
-              <color rgb="00000000"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> </t>
+            <t xml:space="preserve">20228 </t>
           </r>
           <r>
             <rPr>
@@ -1854,7 +1846,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>J. TAPIA (−)</t>
+          <t>J. TAPIA (-)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
